--- a/ai_context/uat/VIFEL_Merge_Pallet_UAT_Test_Script.xlsx
+++ b/ai_context/uat/VIFEL_Merge_Pallet_UAT_Test_Script.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary &amp; Sign-off" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$3:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$3:$I$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Test Cases'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +106,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="9.5"/>
     </font>
@@ -132,7 +138,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -181,6 +187,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001F6F6F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -202,6 +213,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -231,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -255,7 +271,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -279,33 +294,40 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -330,7 +352,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -750,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E31"/>
+  <dimension ref="B2:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -810,7 +832,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -876,7 +898,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>28-Jul-2026</t>
+          <t>02-Aug-2026</t>
         </is>
       </c>
     </row>
@@ -925,200 +947,181 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2.  SCOPE</t>
+          <t>2.  HOW THIS SCRIPT IS ORGANISED</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
     </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Pallet merging (existing, same-receipt, Fixed and Multiple modes); new special pallets; Un-merge; Lot No.; Batch # / Prodcode; partial withdrawal of merge pallets; and pallet-count integrity.</t>
-        </is>
-      </c>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>The 'Test Cases' sheet is grouped by OPERATION TYPE so you test one activity fully before moving on — no jumping back and forth:  (A) Setup &amp; Configuration → (B) Receiving (RR) → (C) Withdrawal (WR) → (D) Reports &amp; Count Integrity.  Do the setup once, then work each coloured section top-to-bottom. Record Actual Result, set Status from the drop-down, and note any issue in Remarks.</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Out of Scope</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Standard Odoo features not changed by this enhancement, printer/hardware setup, and unrelated reports.</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>3.  HOW TO USE THIS SCRIPT</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>3.  STATUS LEGEND</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Behaviour matches the Expected Result.</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
     </row>
-    <row r="21" ht="50" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>1.  Go to the 'Test Cases' sheet.   2.  For each row, read the Scenario Question and perform the 'How to Test' steps in the UAT system.   3.  Record the Actual Result, then set Status to Pass / Fail / Blocked using the drop-down.   4.  Log any issue in Remarks.   5.  When done, complete the 'Summary &amp; Sign-off' sheet for acceptance.</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n"/>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Behaviour differs; log the issue in Remarks.</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>4.  STATUS LEGEND</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Cannot be executed (dependency / defect).</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Not yet run.</t>
+        </is>
+      </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Behaviour matches the Expected Result.</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Behaviour differs; log the issue in Remarks.</t>
-        </is>
-      </c>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>4.  REVISION HISTORY</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Cannot be executed (dependency / defect).</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+    <row r="26">
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Not yet run.</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>5.  REVISION HISTORY</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
           <t>28-Jul-2026</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Elyon Solutions</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Initial scenario-based UAT test script.</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>02-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Elyon Solutions</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Grouped by operation type; added Lot No./Batch #/Prodcode cases.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="C27:E27"/>
+  <mergeCells count="14">
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="C22:E22"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="B25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1140,13 +1143,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
@@ -1155,599 +1158,908 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>MERGE PALLET FEATURE  –  UAT SCENARIO CHECKLIST</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>MERGE PALLET FEATURE  –  UAT SCENARIO CHECKLIST (BY OPERATION TYPE)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Elyon Solutions International Inc.    •    Client: Vifel Ice Plant &amp; Cold Storage, Inc.    •    Version 1.0</t>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Elyon Solutions International Inc.    •    Client: Vifel Ice Plant &amp; Cold Storage, Inc.    •    Version 1.1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Requirement /
 Feature</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Scenario Question (What we are verifying)</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>How to Test</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="76.5" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>MP-01</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>A.  SETUP &amp; CONFIGURATION  (do once)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="76.5" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>MP-A1</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Client Setup</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>When a Vifel client is switched on for merging, do the merge options appear only for that client?</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>On the client's contact, tick 'Can Merge Pallets' in the VIFEL Configuration tab and save. Open a receipt (RR) for this client, then for a different (non-enabled) client.</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>The VIFEL Configuration options (merge mode, PSI types) and the Merge feature appear ONLY for the enabled client; other clients are unaffected.</t>
-        </is>
-      </c>
-      <c r="G4" s="19" t="inlineStr"/>
-      <c r="H4" s="21" t="inlineStr"/>
-      <c r="I4" s="19" t="inlineStr"/>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>MP-02</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Lot No.</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>On the client's contact, tick 'Can Merge Pallets' in the VIFEL Configuration tab and save. Open a receipt for this client, then for a different (non-enabled) client.</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>The VIFEL Configuration options and the Merge feature appear ONLY for the enabled client; other clients are unaffected.</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="19" t="inlineStr"/>
+    </row>
+    <row r="6" ht="76.5" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>MP-A2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Client Setup</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Does the Lot No. really reflect – is the Lot No. typed on a receiving line saved and carried onto stock?</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>Enable 'Show Lot No.' for the client. On an RR line, type a Lot No. Validate the RR. Check the resulting stock (quant) / withdrawal.</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>The Lot No. column shows for this client, the typed value stays on the line, and it is stamped onto the received stock at validation.</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr"/>
-      <c r="H5" s="24" t="inlineStr"/>
-      <c r="I5" s="23" t="inlineStr"/>
-    </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>MP-03</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Batch # / Prodcode</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Can we set the two merge modes — Fixed (one pinned pallet) and Multiple (special PSI types)?</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>For one client set Fixed mode + pin a pallet and a Fixed PSI. For another, tick Multiple Pallet Support and confirm the PSI types (MDGM/SDMG/TDMG/BOC) auto-seed.</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Fixed mode saves the pinned pallet + PSI; Multiple mode shows the special PSI types with descriptions.</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr"/>
+      <c r="H6" s="24" t="inlineStr"/>
+      <c r="I6" s="23" t="inlineStr"/>
+    </row>
+    <row r="7" ht="51.5" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>MP-A3</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Client Setup</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Do the Lot No. and Batch # / Prodcode columns switch on per client from the profile?</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Tick 'Show Lot No.' and 'Show Batch # / Prodcode' for the client, save, and open its Pallet Breakdown.</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>The Lot No. and Batch # columns appear for this client only; other clients don't see them.</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="19" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>B.  RECEIVING  (RR)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>MP-B1</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Merge on Receipt</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>On merge of an existing PSI pallet, does it NOT add a pallet to the count (+0)?</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>On an RR line, click 'Merge Pallet' and pick an existing stocked pallet. Confirm. Compare the received pallet count before and after.</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>The line adopts the target's Pallet Series and location; it is flagged 'Merged'; the received pallet count does NOT increase (+0).</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="21" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10" ht="51.5" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>MP-B2</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Merge on Receipt</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>Does the Batch # really reflect – does the Batch # become a Prodcode (DDMONYYYY + Batch # + Building)?</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>Enable 'Show Batch # / Prodcode'. On an RR line with a production date, type a Batch # (e.g. 99). Validate the RR. Inspect the Prodcode on the stock.</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>The Batch # is saved on the line and, at validation, is converted to a Prodcode in the format day+month+year+Batch#+building short name, e.g. 18MAY202699M.</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="19" t="inlineStr"/>
-    </row>
-    <row r="7" ht="51.5" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>MP-04</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Prodcode at Withdrawal</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>When a line is merged (+0 pallet), do Weight (KG), Quantity and Packs still count in full?</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Review a merged line's Weight (KG), Quantity and Packs after the merge.</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Weight (KG), Quantity and Packs are recorded in full. Only the pallet count is +0; the goods are not lost.</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr"/>
+      <c r="H10" s="24" t="inlineStr"/>
+      <c r="I10" s="23" t="inlineStr"/>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>MP-B3</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Same-Receipt Merge</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>If two lines of the SAME receipt sit on one pallet, is that counted as ONE pallet (+1), not two?</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>On line 1 assign/start a pallet. On line 2 click 'Merge Pallet' and choose line 1's pallet ('On this receipt'). Validate and check the received count.</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>Both lines share one pallet and Pallet Series; the receipt counts them as exactly ONE received pallet (+1). Both lines show 'Merged'.</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="21" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>MP-B4</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Fixed Pallet</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>For a Fixed client, does the FIRST stock onto the empty pinned pallet count as a received pallet (+1), and a later receipt as +0?</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Merge Pallet onto the empty pinned pallet, validate, check the count. Then on a NEW RR merge onto the now-stocked pinned pallet and check again.</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>The first stock counts +1 (it births the pallet); the later receipt merges +0 (no new pallet). Weight/Qty/Packs count in full both times.</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr"/>
+      <c r="H12" s="24" t="inlineStr"/>
+      <c r="I12" s="23" t="inlineStr"/>
+    </row>
+    <row r="13" ht="76.5" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>MP-B5</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>New Special Pallet</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Starting a NEW special pallet (e.g. SDMG) — is it counted as +1, and is its location limited to the receipt's building?</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>On an RR line choose 'Start a New Special Pallet', pick a PSI type, an empty pallet and a location. Try a location in another building, then a valid one; confirm and check the count.</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>Only locations under the receipt's destination building are offered/accepted; the new pallet counts as ONE received pallet (+1).</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr"/>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>MP-B6</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Merge Wizard</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>On withdrawal, does the Prodcode created at receiving show on the WR?</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>Withdraw stock that has a Prodcode. Open the WR Pallet Breakdown and show the 'Prodcode' column.</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>In the merge wizard, if I toggle a second 'Merge Here' pallet, does the first one switch off (only one target)?</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Open Merge Pallet. Toggle 'Merge Here' on one candidate pallet, then on a second candidate.</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Only one 'Merge Here' can be active at a time; selecting a second switches the first off. The system never merges onto two pallets.</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr"/>
+      <c r="H14" s="24" t="inlineStr"/>
+      <c r="I14" s="23" t="inlineStr"/>
+    </row>
+    <row r="15" ht="51.5" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>MP-B7</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Magic Wizard</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Closing the merge dialog with 'X' inside the Magic Wizard — does it return me to the Magic Wizard (not lose my session)?</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>From the Magic Wizard, click Merge on a row (merge dialog opens), then click the 'X' to close it.</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>The Magic Wizard re-opens automatically; the encoding session is not lost.</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="21" t="inlineStr"/>
+      <c r="I15" s="19" t="inlineStr"/>
+    </row>
+    <row r="16" ht="51.5" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>MP-B8</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Lot No. / Batch #</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Does the Lot No. really reflect — is the Lot No. typed on a receiving line saved onto stock?</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>Enter a Lot No. on an RR line. Validate the RR. Open Inventory → the resulting stock (quant).</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>The Lot No. stays on the line and is stamped onto the received stock; it is visible on the quant.</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr"/>
+      <c r="H16" s="24" t="inlineStr"/>
+      <c r="I16" s="23" t="inlineStr"/>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>MP-B9</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Lot No. / Batch #</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Does the Batch # become a Prodcode (DDMONYYYY + Batch # + Building) at validation — WITH the building shortname at the end?</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Enter a Batch # (e.g. 99) on an RR line that has a production date. Validate. Inspect the Prodcode on the stock (quant).</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>The Prodcode is day+month+year+Batch#+building short name, e.g. 18MAY202699M — the building short name IS present at the end for every building.</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr"/>
+      <c r="H17" s="21" t="inlineStr"/>
+      <c r="I17" s="19" t="inlineStr"/>
+    </row>
+    <row r="18" ht="51.5" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>MP-B10</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Column Order</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Are the Lot No., Batch # and Prodcode columns shown right after the Container # column?</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>Open an RR Pallet Breakdown and look at the column order.</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Lot No. / Batch # / Prodcode appear immediately after Container #, matching the Magic Wizard layout.</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr"/>
+      <c r="H18" s="24" t="inlineStr"/>
+      <c r="I18" s="23" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>C.  WITHDRAWAL  (WR)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>MP-C1</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Partial Withdrawal</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>On WR, can a merge pallet be PARTIALLY withdrawn, and does it count -0 (only -1 when fully emptied)?</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Create a WR that withdraws SOME of the products on a merge pallet, leaving others. Validate. Then fully empty the pallet on another WR.</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>The partial withdrawal is allowed (no 'still has available quantity' block) and counts -0. The pallet counts -1 only when fully emptied.</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr"/>
+      <c r="H20" s="21" t="inlineStr"/>
+      <c r="I20" s="19" t="inlineStr"/>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>MP-C2</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Un-merge</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Can a merged / shared line be Un-merged on a receipt, and does the pallet count stay correct?</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>On a line that shows 'Merged', click 'Un-merge'. Observe the line and the pallet; re-check the count.</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>The line is peeled off to its own blank pallet (re-assign a series); the other line keeps the pallet; the pallet count stays correct.</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr"/>
+      <c r="H21" s="24" t="inlineStr"/>
+      <c r="I21" s="23" t="inlineStr"/>
+    </row>
+    <row r="22" ht="51.5" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>MP-C3</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Lot No. on WR</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>On withdrawal, does the Lot No. that was set at receiving get PULLED onto the WR Pallet Breakdown?</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Withdraw stock that had a Lot No. set at receiving. Open the WR Pallet Breakdown and show the Lot No. column.</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>The Lot No. frozen at receiving is displayed (read-only) on the matching withdrawal line — it is no longer blank.</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr"/>
+      <c r="H22" s="21" t="inlineStr"/>
+      <c r="I22" s="19" t="inlineStr"/>
+    </row>
+    <row r="23" ht="51.5" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>MP-C4</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Prodcode on WR</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>On withdrawal, does the Prodcode created at receiving show on the WR Pallet Breakdown?</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>Withdraw stock that has a Prodcode. Open the WR Pallet Breakdown and show the Prodcode column.</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>The Prodcode frozen at receiving is displayed (read-only) on the matching withdrawal line.</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="24" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr"/>
-    </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>MP-05</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Merge onto Existing Pallet</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr"/>
+      <c r="H23" s="24" t="inlineStr"/>
+      <c r="I23" s="23" t="inlineStr"/>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>MP-C5</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Multi-truck</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>For a pallet shared across trucks, does it count on the truck that EMPTIES it (not the first truck)?</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Split one pallet across two WRs (one leaves stock, the next takes the rest). Validate both; check which WR counts the pallet.</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>The pallet counts once, on the WR whose validation leaves the pallet empty; the truck that left stock counts it -0.</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr"/>
+      <c r="H24" s="21" t="inlineStr"/>
+      <c r="I24" s="19" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>D.  REPORTS &amp; COUNT INTEGRITY</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="51.5" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>MP-D1</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Count Integrity</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>On merge of an existing PSI pallet, does it NOT add a pallet to the count (+0)?</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>On an RR line, click 'Merge Pallet' and pick an existing stocked pallet. Confirm. Compare the received pallet count before and after.</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>The line adopts the target's Pallet Series and location; it is flagged 'Merged'; and the received pallet count does NOT increase (+0).</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="21" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr"/>
-    </row>
-    <row r="9" ht="51.5" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>MP-06</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>Merge – Weight/Qty</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Does a merge / shared pallet count as exactly ONE pallet end-to-end (receipt, ledger and reports)?</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>For a merge pallet, review the RR received count, the pallet-kilos (PKR) ledger, and the WR/RR printout.</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>The merge pallet is counted as exactly ONE pallet in the receipt, the ledger, and the printed reports — all agree.</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr"/>
+      <c r="H26" s="21" t="inlineStr"/>
+      <c r="I26" s="19" t="inlineStr"/>
+    </row>
+    <row r="27" ht="51.5" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>MP-D2</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>When a line is merged (+0 pallet), do Weight (KG), Quantity and Packs still count in full?</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>Review a merged line's Weight (KG), Quantity and Packs after the merge.</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>Weight (KG), Quantity and Packs are recorded in full. Only the pallet count is +0; the goods are not lost.</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr"/>
-      <c r="H9" s="24" t="inlineStr"/>
-      <c r="I9" s="23" t="inlineStr"/>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>MP-07</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Same-Receipt Merge</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>If two lines of the SAME receipt sit on one pallet, is that counted as ONE pallet (+1), not two?</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>On line 1 assign/start a pallet. On line 2 click 'Merge Pallet' and choose line 1's pallet ('On this receipt'). Validate and check the received pallet count.</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>Both lines share one pallet and Pallet Series; the receipt counts them as exactly ONE received pallet (+1). Both lines show 'Merged'.</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="21" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>MP-08</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Fixed Pallet – First Stock</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>For a Fixed client, does the FIRST stock onto the empty pinned pallet count as a received pallet (+1)?</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>Configure Fixed mode with a pinned pallet (empty). On an RR line, Merge Pallet onto the pinned pallet. Validate. Check the count.</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>The first stock births the pinned pallet and is counted as ONE received pallet (+1).</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr"/>
-      <c r="H11" s="24" t="inlineStr"/>
-      <c r="I11" s="23" t="inlineStr"/>
-    </row>
-    <row r="12" ht="51.5" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>MP-09</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Fixed Pallet – Later Merge</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>For the SAME pinned pallet, does a later receipt merge onto it count as +0 (no new pallet)?</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>On a NEW RR for the same client, Merge Pallet onto the now-stocked pinned pallet. Validate. Check the count.</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>The later line merges (+0); the pinned pallet is not counted again. Weight/Quantity/Packs still count in full.</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr"/>
-      <c r="I12" s="19" t="inlineStr"/>
-    </row>
-    <row r="13" ht="76.5" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>MP-10</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Un-merge</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Do the WR/RR pallet-count printouts match the pallet-kilos ledger (no drift)?</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>Print a WR summary / per-pallet report and compare its pallet count to the PKR ledger for the same document.</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>The printed pallet count equals the ledger figure and does not change on re-print.</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr"/>
+      <c r="H27" s="24" t="inlineStr"/>
+      <c r="I27" s="23" t="inlineStr"/>
+    </row>
+    <row r="28" ht="51.5" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>MP-D3</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Stock View</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Can Lot No., Batch # and Prodcode be looked up in the Inventory (stock) view?</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>In Inventory → Stock, enable the optional Lot No., Batch # and Prodcode columns.</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>All three columns are available in the stock view and show the values frozen at receiving.</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr"/>
+      <c r="H28" s="21" t="inlineStr"/>
+      <c r="I28" s="19" t="inlineStr"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>MP-D4</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Can a merged / shared line be Un-merged, and does the pallet count stay correct?</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>On a line that shows 'Merged', click 'Un-merge'. Observe the line and the pallet, then re-check the received count.</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>The line is peeled off to its own blank pallet (re-assign a Pallet Series); the other line keeps the pallet; the pallet is STILL counted correctly (no double count, no loss).</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr"/>
-      <c r="H13" s="24" t="inlineStr"/>
-      <c r="I13" s="23" t="inlineStr"/>
-    </row>
-    <row r="14" ht="76.5" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>MP-11</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>New Special Pallet</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>Starting a NEW special pallet (e.g. SDMG) – is it counted as +1, and is its location limited to the receipt's building?</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>On an RR line choose 'Start a New Special Pallet', pick a PSI type, an empty pallet and a location. Try a location in another building, then a valid one. Confirm and check the count.</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>Only locations under the receipt's destination building are offered/accepted; the new pallet is counted as ONE received pallet (+1).</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr"/>
-      <c r="H14" s="21" t="inlineStr"/>
-      <c r="I14" s="19" t="inlineStr"/>
-    </row>
-    <row r="15" ht="76.5" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>MP-12</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>Partial Withdrawal</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>On WR, can a merge pallet be PARTIALLY withdrawn, and does it count -0 (only -1 when fully emptied)?</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>Create a WR that withdraws SOME of the products on a merge pallet, leaving others. Validate. Then fully empty the pallet on another WR.</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>The partial withdrawal is allowed (no 'incomplete package / still has available quantity' block) and counts -0. The pallet counts -1 only when it is fully emptied.</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr"/>
-      <c r="H15" s="24" t="inlineStr"/>
-      <c r="I15" s="23" t="inlineStr"/>
-    </row>
-    <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>MP-13</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>Single Merge Target</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>In the merge wizard, if I toggle a second 'Merge Here' pallet, does the first one switch off (only one target)?</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Open Merge Pallet. Toggle 'Merge Here' on one candidate pallet, then toggle it on a second candidate.</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>Only one 'Merge Here' can be active at a time; selecting a second automatically switches the first off. The system never merges onto two pallets.</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr"/>
-      <c r="H16" s="21" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr"/>
-    </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>MP-14</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Repeated Merge Validates</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>Does a second (and later) merge onto the same pallet validate without a false 'Pallet Series already in stock' error?</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>Merge a second, then a third receipt onto the same pallet / Pallet Series. Validate each receipt.</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>Each receipt validates successfully; merged lines are exempt from the duplicate-series check, so no false error is raised.</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="inlineStr"/>
-      <c r="H17" s="24" t="inlineStr"/>
-      <c r="I17" s="23" t="inlineStr"/>
-    </row>
-    <row r="18" ht="64" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>MP-15</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>Plug-and-Play</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>After installing the feature, do the existing Pallet Breakdown workflow buttons still work?</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>Open an RR Pallet Breakdown and use the existing buttons (Verify Transfer, Assign Pallet Series, Assign Locations, Auto-Fill, Delete).</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>All existing workflow buttons remain present and functional; the feature is additive and does not break current operations.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr"/>
-      <c r="H18" s="21" t="inlineStr"/>
-      <c r="I18" s="19" t="inlineStr"/>
+      <c r="G29" s="23" t="inlineStr"/>
+      <c r="H29" s="24" t="inlineStr"/>
+      <c r="I29" s="23" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I18"/>
-  <mergeCells count="2">
+  <autoFilter ref="A3:I29"/>
+  <mergeCells count="6">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H18">
+  <conditionalFormatting sqref="H5">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -1761,8 +2073,302 @@
       <formula>"Not Executed"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="39" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="40" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="cellIs" priority="41" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="43" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="44" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="cellIs" priority="45" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="46" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="47" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="48" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="cellIs" priority="49" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="50" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="51" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="52" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="cellIs" priority="53" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="54" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="55" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="56" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21">
+    <cfRule type="cellIs" priority="57" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="58" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="59" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="60" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22">
+    <cfRule type="cellIs" priority="61" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="62" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="63" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="64" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
+    <cfRule type="cellIs" priority="65" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="66" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="67" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="68" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="cellIs" priority="69" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="70" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="71" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="72" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="cellIs" priority="73" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="74" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="75" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="76" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="cellIs" priority="77" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="78" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="79" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="80" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="cellIs" priority="81" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="82" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="83" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="84" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="cellIs" priority="85" operator="equal" dxfId="0">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="86" operator="equal" dxfId="1">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="87" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="88" operator="equal" dxfId="3">
+      <formula>"Not Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H4:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Select Pass, Fail, Blocked or Not Executed." promptTitle="Status" prompt="Choose the execution result" type="list">
+    <dataValidation sqref="H5 H6 H7 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H20 H21 H22 H23 H24 H26 H27 H28 H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Select Pass, Fail, Blocked or Not Executed." type="list">
       <formula1>"Pass,Fail,Blocked,Not Executed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1798,42 +2404,42 @@
   </cols>
   <sheetData>
     <row r="2" ht="24" customHeight="1">
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>EXECUTION SUMMARY &amp; ACCEPTANCE SIGN-OFF</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>RESULT</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>% OF TOTAL</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1841,84 +2447,84 @@
       <c r="E5" s="5" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C6" s="27">
-        <f>COUNTIF('Test Cases'!H4:H18,"Pass")</f>
+      <c r="C6" s="29">
+        <f>COUNTIF('Test Cases'!H5,"Pass")+COUNTIF('Test Cases'!H6,"Pass")+COUNTIF('Test Cases'!H7,"Pass")+COUNTIF('Test Cases'!H9,"Pass")+COUNTIF('Test Cases'!H10,"Pass")+COUNTIF('Test Cases'!H11,"Pass")+COUNTIF('Test Cases'!H12,"Pass")+COUNTIF('Test Cases'!H13,"Pass")+COUNTIF('Test Cases'!H14,"Pass")+COUNTIF('Test Cases'!H15,"Pass")+COUNTIF('Test Cases'!H16,"Pass")+COUNTIF('Test Cases'!H17,"Pass")+COUNTIF('Test Cases'!H18,"Pass")+COUNTIF('Test Cases'!H20,"Pass")+COUNTIF('Test Cases'!H21,"Pass")+COUNTIF('Test Cases'!H22,"Pass")+COUNTIF('Test Cases'!H23,"Pass")+COUNTIF('Test Cases'!H24,"Pass")+COUNTIF('Test Cases'!H26,"Pass")+COUNTIF('Test Cases'!H27,"Pass")+COUNTIF('Test Cases'!H28,"Pass")+COUNTIF('Test Cases'!H29,"Pass")</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="32">
         <f>IF($C$5=0,0,C6/$C$5)</f>
         <v/>
       </c>
       <c r="E6" s="5" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="C7" s="27">
-        <f>COUNTIF('Test Cases'!H4:H18,"Fail")</f>
+      <c r="C7" s="29">
+        <f>COUNTIF('Test Cases'!H5,"Fail")+COUNTIF('Test Cases'!H6,"Fail")+COUNTIF('Test Cases'!H7,"Fail")+COUNTIF('Test Cases'!H9,"Fail")+COUNTIF('Test Cases'!H10,"Fail")+COUNTIF('Test Cases'!H11,"Fail")+COUNTIF('Test Cases'!H12,"Fail")+COUNTIF('Test Cases'!H13,"Fail")+COUNTIF('Test Cases'!H14,"Fail")+COUNTIF('Test Cases'!H15,"Fail")+COUNTIF('Test Cases'!H16,"Fail")+COUNTIF('Test Cases'!H17,"Fail")+COUNTIF('Test Cases'!H18,"Fail")+COUNTIF('Test Cases'!H20,"Fail")+COUNTIF('Test Cases'!H21,"Fail")+COUNTIF('Test Cases'!H22,"Fail")+COUNTIF('Test Cases'!H23,"Fail")+COUNTIF('Test Cases'!H24,"Fail")+COUNTIF('Test Cases'!H26,"Fail")+COUNTIF('Test Cases'!H27,"Fail")+COUNTIF('Test Cases'!H28,"Fail")+COUNTIF('Test Cases'!H29,"Fail")</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="32">
         <f>IF($C$5=0,0,C7/$C$5)</f>
         <v/>
       </c>
       <c r="E7" s="5" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="C8" s="27">
-        <f>COUNTIF('Test Cases'!H4:H18,"Blocked")</f>
+      <c r="C8" s="29">
+        <f>COUNTIF('Test Cases'!H5,"Blocked")+COUNTIF('Test Cases'!H6,"Blocked")+COUNTIF('Test Cases'!H7,"Blocked")+COUNTIF('Test Cases'!H9,"Blocked")+COUNTIF('Test Cases'!H10,"Blocked")+COUNTIF('Test Cases'!H11,"Blocked")+COUNTIF('Test Cases'!H12,"Blocked")+COUNTIF('Test Cases'!H13,"Blocked")+COUNTIF('Test Cases'!H14,"Blocked")+COUNTIF('Test Cases'!H15,"Blocked")+COUNTIF('Test Cases'!H16,"Blocked")+COUNTIF('Test Cases'!H17,"Blocked")+COUNTIF('Test Cases'!H18,"Blocked")+COUNTIF('Test Cases'!H20,"Blocked")+COUNTIF('Test Cases'!H21,"Blocked")+COUNTIF('Test Cases'!H22,"Blocked")+COUNTIF('Test Cases'!H23,"Blocked")+COUNTIF('Test Cases'!H24,"Blocked")+COUNTIF('Test Cases'!H26,"Blocked")+COUNTIF('Test Cases'!H27,"Blocked")+COUNTIF('Test Cases'!H28,"Blocked")+COUNTIF('Test Cases'!H29,"Blocked")</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="32">
         <f>IF($C$5=0,0,C8/$C$5)</f>
         <v/>
       </c>
       <c r="E8" s="5" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="C9" s="27">
-        <f>COUNTIF('Test Cases'!H4:H18,"Not Executed")+COUNTBLANK('Test Cases'!H4:H18)</f>
+      <c r="C9" s="29">
+        <f>22-(COUNTIF('Test Cases'!H5,"Pass")+COUNTIF('Test Cases'!H6,"Pass")+COUNTIF('Test Cases'!H7,"Pass")+COUNTIF('Test Cases'!H9,"Pass")+COUNTIF('Test Cases'!H10,"Pass")+COUNTIF('Test Cases'!H11,"Pass")+COUNTIF('Test Cases'!H12,"Pass")+COUNTIF('Test Cases'!H13,"Pass")+COUNTIF('Test Cases'!H14,"Pass")+COUNTIF('Test Cases'!H15,"Pass")+COUNTIF('Test Cases'!H16,"Pass")+COUNTIF('Test Cases'!H17,"Pass")+COUNTIF('Test Cases'!H18,"Pass")+COUNTIF('Test Cases'!H20,"Pass")+COUNTIF('Test Cases'!H21,"Pass")+COUNTIF('Test Cases'!H22,"Pass")+COUNTIF('Test Cases'!H23,"Pass")+COUNTIF('Test Cases'!H24,"Pass")+COUNTIF('Test Cases'!H26,"Pass")+COUNTIF('Test Cases'!H27,"Pass")+COUNTIF('Test Cases'!H28,"Pass")+COUNTIF('Test Cases'!H29,"Pass")+COUNTIF('Test Cases'!H5,"Fail")+COUNTIF('Test Cases'!H6,"Fail")+COUNTIF('Test Cases'!H7,"Fail")+COUNTIF('Test Cases'!H9,"Fail")+COUNTIF('Test Cases'!H10,"Fail")+COUNTIF('Test Cases'!H11,"Fail")+COUNTIF('Test Cases'!H12,"Fail")+COUNTIF('Test Cases'!H13,"Fail")+COUNTIF('Test Cases'!H14,"Fail")+COUNTIF('Test Cases'!H15,"Fail")+COUNTIF('Test Cases'!H16,"Fail")+COUNTIF('Test Cases'!H17,"Fail")+COUNTIF('Test Cases'!H18,"Fail")+COUNTIF('Test Cases'!H20,"Fail")+COUNTIF('Test Cases'!H21,"Fail")+COUNTIF('Test Cases'!H22,"Fail")+COUNTIF('Test Cases'!H23,"Fail")+COUNTIF('Test Cases'!H24,"Fail")+COUNTIF('Test Cases'!H26,"Fail")+COUNTIF('Test Cases'!H27,"Fail")+COUNTIF('Test Cases'!H28,"Fail")+COUNTIF('Test Cases'!H29,"Fail")+COUNTIF('Test Cases'!H5,"Blocked")+COUNTIF('Test Cases'!H6,"Blocked")+COUNTIF('Test Cases'!H7,"Blocked")+COUNTIF('Test Cases'!H9,"Blocked")+COUNTIF('Test Cases'!H10,"Blocked")+COUNTIF('Test Cases'!H11,"Blocked")+COUNTIF('Test Cases'!H12,"Blocked")+COUNTIF('Test Cases'!H13,"Blocked")+COUNTIF('Test Cases'!H14,"Blocked")+COUNTIF('Test Cases'!H15,"Blocked")+COUNTIF('Test Cases'!H16,"Blocked")+COUNTIF('Test Cases'!H17,"Blocked")+COUNTIF('Test Cases'!H18,"Blocked")+COUNTIF('Test Cases'!H20,"Blocked")+COUNTIF('Test Cases'!H21,"Blocked")+COUNTIF('Test Cases'!H22,"Blocked")+COUNTIF('Test Cases'!H23,"Blocked")+COUNTIF('Test Cases'!H24,"Blocked")+COUNTIF('Test Cases'!H26,"Blocked")+COUNTIF('Test Cases'!H27,"Blocked")+COUNTIF('Test Cases'!H28,"Blocked")+COUNTIF('Test Cases'!H29,"Blocked"))</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="32">
         <f>IF($C$5=0,0,C9/$C$5)</f>
         <v/>
       </c>
       <c r="E9" s="5" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Overall Pass Rate</t>
         </is>
       </c>
-      <c r="C10" s="35">
-        <f>IF($C$5=0,0,COUNTIF('Test Cases'!H4:H18,"Pass")/$C$5)</f>
+      <c r="C10" s="37">
+        <f>IF($C$5=0,0,(COUNTIF('Test Cases'!H5,"Pass")+COUNTIF('Test Cases'!H6,"Pass")+COUNTIF('Test Cases'!H7,"Pass")+COUNTIF('Test Cases'!H9,"Pass")+COUNTIF('Test Cases'!H10,"Pass")+COUNTIF('Test Cases'!H11,"Pass")+COUNTIF('Test Cases'!H12,"Pass")+COUNTIF('Test Cases'!H13,"Pass")+COUNTIF('Test Cases'!H14,"Pass")+COUNTIF('Test Cases'!H15,"Pass")+COUNTIF('Test Cases'!H16,"Pass")+COUNTIF('Test Cases'!H17,"Pass")+COUNTIF('Test Cases'!H18,"Pass")+COUNTIF('Test Cases'!H20,"Pass")+COUNTIF('Test Cases'!H21,"Pass")+COUNTIF('Test Cases'!H22,"Pass")+COUNTIF('Test Cases'!H23,"Pass")+COUNTIF('Test Cases'!H24,"Pass")+COUNTIF('Test Cases'!H26,"Pass")+COUNTIF('Test Cases'!H27,"Pass")+COUNTIF('Test Cases'!H28,"Pass")+COUNTIF('Test Cases'!H29,"Pass"))/$C$5)</f>
         <v/>
       </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>OVERALL UAT ASSESSMENT</t>
         </is>
@@ -1928,7 +2534,7 @@
       <c r="E13" s="5" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>☐   Accepted</t>
         </is>
@@ -1938,7 +2544,7 @@
       <c r="E14" s="5" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>☐   Accepted with Conditions</t>
         </is>
@@ -1948,7 +2554,7 @@
       <c r="E15" s="5" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>☐   Rejected</t>
         </is>
@@ -1958,7 +2564,7 @@
       <c r="E16" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Remarks / Conditions:</t>
         </is>
@@ -1996,29 +2602,29 @@
       <c r="E23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C24" s="39" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D24" s="39" t="inlineStr">
+      <c r="D24" s="41" t="inlineStr">
         <is>
           <t>Signature</t>
         </is>
       </c>
-      <c r="E24" s="39" t="inlineStr">
+      <c r="E24" s="41" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="42" t="inlineStr">
         <is>
           <t>Prepared by (Elyon)</t>
         </is>
@@ -2028,7 +2634,7 @@
       <c r="E25" s="5" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>Tested by (Vifel)</t>
         </is>
@@ -2038,7 +2644,7 @@
       <c r="E26" s="5" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="42" t="inlineStr">
         <is>
           <t>Reviewed by (Vifel)</t>
         </is>
@@ -2048,7 +2654,7 @@
       <c r="E27" s="5" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>Approved by (Vifel)</t>
         </is>
